--- a/tools/importer/reports/import-procedure-landing.report.xlsx
+++ b/tools/importer/reports/import-procedure-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,31 @@
     <t>procedure-landing</t>
   </si>
   <si>
-    <t>2026-04-30T17:15:17.439Z</t>
+    <t>2026-04-30T18:17:00.821Z</t>
   </si>
   <si>
     <t>DART Direct Anterior Reconstructive Technology | Stryker</t>
   </si>
   <si>
     <t>https://www.stryker.com/us/en/joint-replacement/procedures/dart-direct-anterior-reconstructive-technology.html</t>
+  </si>
+  <si>
+    <t>us/en/joint-replacement/procedures/direct-superior-approach.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","section-nav","columns","columns","columns","cards","cards","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>us/en/joint-replacement/procedures/direct-superior-approach</t>
+  </si>
+  <si>
+    <t>2026-04-30T18:16:17.427Z</t>
+  </si>
+  <si>
+    <t>Direct Superior Approach | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/joint-replacement/procedures/direct-superior-approach.html</t>
   </si>
 </sst>
 </file>
@@ -447,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -508,6 +526,32 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-procedure-landing.report.xlsx
+++ b/tools/importer/reports/import-procedure-landing.report.xlsx
@@ -70,7 +70,7 @@
     <t>us/en/joint-replacement/procedures/direct-superior-approach</t>
   </si>
   <si>
-    <t>2026-04-30T18:16:17.427Z</t>
+    <t>2026-05-01T17:50:36.503Z</t>
   </si>
   <si>
     <t>Direct Superior Approach | Stryker</t>
